--- a/public/lohc-dashboard/demo/lohc_demo_line9.xlsx
+++ b/public/lohc-dashboard/demo/lohc_demo_line9.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA11"/>
+  <dimension ref="A1:CA16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -828,55 +828,55 @@
         <v>1.261456393374505</v>
       </c>
       <c r="E2" t="n">
-        <v>826.494745</v>
+        <v>860.3123399999999</v>
       </c>
       <c r="F2" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="G2" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="H2" t="n">
-        <v>19.49</v>
+        <v>15</v>
       </c>
       <c r="I2" t="n">
         <v>1500</v>
       </c>
       <c r="J2" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="K2" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="L2" t="n">
         <v>1.034</v>
       </c>
       <c r="M2" t="n">
-        <v>642.22253</v>
+        <v>701.938526</v>
       </c>
       <c r="N2" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="O2" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="P2" t="n">
         <v>1.027</v>
       </c>
       <c r="Q2" t="n">
-        <v>380.211473</v>
+        <v>440.087704</v>
       </c>
       <c r="R2" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="S2" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="T2" t="n">
         <v>1.02</v>
       </c>
       <c r="U2" t="n">
-        <v>206.073649</v>
+        <v>208.667799</v>
       </c>
       <c r="V2" t="n">
         <v>54.6795848</v>
@@ -888,7 +888,7 @@
         <v>50</v>
       </c>
       <c r="Y2" t="n">
-        <v>480.193305</v>
+        <v>600.701162</v>
       </c>
       <c r="Z2" t="n">
         <v>70</v>
@@ -900,34 +900,34 @@
         <v>50</v>
       </c>
       <c r="AC2" t="n">
-        <v>480.193305</v>
+        <v>600.701162</v>
       </c>
       <c r="AD2" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AE2" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AF2" t="n">
         <v>1.013</v>
       </c>
       <c r="AG2" t="n">
-        <v>191.441313</v>
+        <v>194.916997</v>
       </c>
       <c r="AH2" t="n">
-        <v>-258041.636</v>
+        <v>-241187.022</v>
       </c>
       <c r="AI2" t="n">
-        <v>-47296.0762</v>
+        <v>-54559.3021</v>
       </c>
       <c r="AJ2" t="n">
         <v>32.9836374</v>
       </c>
       <c r="AK2" t="n">
-        <v>397.973609</v>
+        <v>400.497918</v>
       </c>
       <c r="AL2" t="n">
-        <v>-304906.754</v>
+        <v>-295312.842</v>
       </c>
       <c r="AM2" t="n">
         <v>15.3204152</v>
@@ -939,13 +939,13 @@
         <v>50</v>
       </c>
       <c r="AP2" t="n">
-        <v>480.193305</v>
+        <v>600.701162</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-2510.55122</v>
+        <v>-2165.59136</v>
       </c>
       <c r="AR2" t="n">
-        <v>-12582567.8</v>
+        <v>-12302454</v>
       </c>
       <c r="AS2" t="n">
         <v>15.3204152</v>
@@ -957,7 +957,7 @@
         <v>50</v>
       </c>
       <c r="AV2" t="n">
-        <v>426.21873</v>
+        <v>556.977748</v>
       </c>
       <c r="AW2" t="n">
         <v>0.317881664</v>
@@ -981,37 +981,37 @@
         <v>1.12952642</v>
       </c>
       <c r="BD2" t="n">
-        <v>287.336499</v>
+        <v>399.773402</v>
       </c>
       <c r="BE2" t="n">
         <v>0.317881664</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.012949797</v>
+        <v>0.0129498979</v>
       </c>
       <c r="BG2" t="n">
         <v>1.12952642</v>
       </c>
       <c r="BH2" t="n">
-        <v>87.6177972</v>
+        <v>134.370922</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.59999176e-06</v>
+        <v>1.35416246e-09</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.74999805</v>
+        <v>0.749999999</v>
       </c>
       <c r="BK2" t="n">
         <v>0.317881664</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.012949797</v>
+        <v>0.0129498979</v>
       </c>
       <c r="BM2" t="n">
         <v>1.12952642</v>
       </c>
       <c r="BN2" t="n">
-        <v>426.21873</v>
+        <v>556.977752</v>
       </c>
       <c r="BO2" t="n">
         <v>70</v>
@@ -1023,7 +1023,7 @@
         <v>50.07</v>
       </c>
       <c r="BR2" t="n">
-        <v>173.837024</v>
+        <v>179.170434</v>
       </c>
       <c r="BS2" t="n">
         <v>70</v>
@@ -1035,7 +1035,7 @@
         <v>50.05</v>
       </c>
       <c r="BV2" t="n">
-        <v>192.398771</v>
+        <v>195.989911</v>
       </c>
       <c r="BW2" t="n">
         <v>70</v>
@@ -1050,84 +1050,84 @@
         <v>264.0032</v>
       </c>
       <c r="CA2" t="n">
-        <v>11.53</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9872338750267784</v>
+        <v>0.8574379349505404</v>
       </c>
       <c r="C3" t="n">
-        <v>3.788177726481099</v>
+        <v>4.885136690673612</v>
       </c>
       <c r="D3" t="n">
-        <v>6.758355283713234</v>
+        <v>4.762764725089321</v>
       </c>
       <c r="E3" t="n">
-        <v>1784.35111</v>
+        <v>3517.02956</v>
       </c>
       <c r="F3" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="G3" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="H3" t="n">
-        <v>19.49</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
         <v>1500</v>
       </c>
       <c r="J3" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="K3" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="L3" t="n">
         <v>1.034</v>
       </c>
       <c r="M3" t="n">
-        <v>642.22253</v>
+        <v>701.938526</v>
       </c>
       <c r="N3" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="O3" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="P3" t="n">
         <v>1.027</v>
       </c>
       <c r="Q3" t="n">
-        <v>380.216394</v>
+        <v>440.135916</v>
       </c>
       <c r="R3" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="S3" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="T3" t="n">
         <v>1.02</v>
       </c>
       <c r="U3" t="n">
-        <v>205.910642</v>
+        <v>208.172282</v>
       </c>
       <c r="V3" t="n">
-        <v>69.10637130000001</v>
+        <v>60.0206554</v>
       </c>
       <c r="W3" t="n">
-        <v>3.83598652</v>
+        <v>3.33165266</v>
       </c>
       <c r="X3" t="n">
         <v>50</v>
       </c>
       <c r="Y3" t="n">
-        <v>480.20505</v>
+        <v>600.773998</v>
       </c>
       <c r="Z3" t="n">
         <v>70</v>
@@ -1139,118 +1139,118 @@
         <v>50</v>
       </c>
       <c r="AC3" t="n">
-        <v>480.20505</v>
+        <v>600.773998</v>
       </c>
       <c r="AD3" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AE3" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AF3" t="n">
         <v>1.013</v>
       </c>
       <c r="AG3" t="n">
-        <v>191.23576</v>
+        <v>194.319249</v>
       </c>
       <c r="AH3" t="n">
-        <v>-258041.636</v>
+        <v>-241187.022</v>
       </c>
       <c r="AI3" t="n">
-        <v>-46950.0777</v>
+        <v>-53560.4526</v>
       </c>
       <c r="AJ3" t="n">
         <v>32.9836374</v>
       </c>
       <c r="AK3" t="n">
-        <v>397.853033</v>
+        <v>400.150479</v>
       </c>
       <c r="AL3" t="n">
-        <v>-304560.877</v>
+        <v>-294314.34</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.893628748</v>
+        <v>9.97934455</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.0496039333</v>
+        <v>0.553937799</v>
       </c>
       <c r="AO3" t="n">
         <v>50</v>
       </c>
       <c r="AP3" t="n">
-        <v>480.20505</v>
+        <v>600.773998</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-2510.51468</v>
+        <v>-2165.39785</v>
       </c>
       <c r="AR3" t="n">
-        <v>-12582540.3</v>
+        <v>-12302284.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.893628748</v>
+        <v>9.97934455</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.0496039333</v>
+        <v>0.553937799</v>
       </c>
       <c r="AU3" t="n">
         <v>50</v>
       </c>
       <c r="AV3" t="n">
-        <v>263.977846</v>
+        <v>417.46222</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.70307688</v>
+        <v>1.20019652</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0173450331</v>
+        <v>0.0122234343</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.78817773</v>
+        <v>4.88513669</v>
       </c>
       <c r="AZ3" t="n">
         <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.70307688</v>
+        <v>1.20019652</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.0173450331</v>
+        <v>0.0122234343</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.78817773</v>
+        <v>4.88513669</v>
       </c>
       <c r="BD3" t="n">
-        <v>123.079923</v>
+        <v>168.43424</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.70307688</v>
+        <v>1.20019652</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.0277228966</v>
+        <v>0.0487428861</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.78817773</v>
+        <v>4.88513669</v>
       </c>
       <c r="BH3" t="n">
-        <v>161.829949</v>
+        <v>227.51794</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.500876423</v>
+        <v>0.00103161084</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.374342683</v>
+        <v>0.749226292</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.70307688</v>
+        <v>1.20019652</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0277228966</v>
+        <v>0.0487428861</v>
       </c>
       <c r="BM3" t="n">
-        <v>3.78817773</v>
+        <v>4.88513669</v>
       </c>
       <c r="BN3" t="n">
-        <v>263.897237</v>
+        <v>417.274522</v>
       </c>
       <c r="BO3" t="n">
         <v>70</v>
@@ -1262,7 +1262,7 @@
         <v>50.07</v>
       </c>
       <c r="BR3" t="n">
-        <v>173.577187</v>
+        <v>178.44819</v>
       </c>
       <c r="BS3" t="n">
         <v>70</v>
@@ -1274,7 +1274,7 @@
         <v>50.05</v>
       </c>
       <c r="BV3" t="n">
-        <v>192.198163</v>
+        <v>195.405678</v>
       </c>
       <c r="BW3" t="n">
         <v>70</v>
@@ -1289,84 +1289,84 @@
         <v>264.0032</v>
       </c>
       <c r="CA3" t="n">
-        <v>11.86</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8027532074327079</v>
+        <v>0.9042324940752052</v>
       </c>
       <c r="C4" t="n">
-        <v>1.59658948976505</v>
+        <v>1.929979659635996</v>
       </c>
       <c r="D4" t="n">
-        <v>11.89134823518332</v>
+        <v>8.339116572269141</v>
       </c>
       <c r="E4" t="n">
-        <v>5249.20476</v>
+        <v>4225.65749</v>
       </c>
       <c r="F4" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="G4" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="H4" t="n">
-        <v>19.49</v>
+        <v>15</v>
       </c>
       <c r="I4" t="n">
         <v>1500</v>
       </c>
       <c r="J4" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="K4" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="L4" t="n">
         <v>1.034</v>
       </c>
       <c r="M4" t="n">
-        <v>642.22253</v>
+        <v>701.938526</v>
       </c>
       <c r="N4" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="O4" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="P4" t="n">
         <v>1.027</v>
       </c>
       <c r="Q4" t="n">
-        <v>380.228395</v>
+        <v>440.170707</v>
       </c>
       <c r="R4" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="S4" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="T4" t="n">
         <v>1.02</v>
       </c>
       <c r="U4" t="n">
-        <v>205.317856</v>
+        <v>207.990695</v>
       </c>
       <c r="V4" t="n">
-        <v>56.1927245</v>
+        <v>63.2962746</v>
       </c>
       <c r="W4" t="n">
-        <v>3.1191702</v>
+        <v>3.51347715</v>
       </c>
       <c r="X4" t="n">
         <v>50</v>
       </c>
       <c r="Y4" t="n">
-        <v>480.233479</v>
+        <v>600.825106</v>
       </c>
       <c r="Z4" t="n">
         <v>70</v>
@@ -1378,118 +1378,118 @@
         <v>50</v>
       </c>
       <c r="AC4" t="n">
-        <v>480.233479</v>
+        <v>600.825106</v>
       </c>
       <c r="AD4" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AE4" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AF4" t="n">
         <v>1.013</v>
       </c>
       <c r="AG4" t="n">
-        <v>190.488092</v>
+        <v>194.103506</v>
       </c>
       <c r="AH4" t="n">
-        <v>-258041.636</v>
+        <v>-241187.022</v>
       </c>
       <c r="AI4" t="n">
-        <v>-45705.7607</v>
+        <v>-53296.7834</v>
       </c>
       <c r="AJ4" t="n">
         <v>32.9836374</v>
       </c>
       <c r="AK4" t="n">
-        <v>397.41857</v>
+        <v>400.058822</v>
       </c>
       <c r="AL4" t="n">
-        <v>-303316.994</v>
+        <v>-294050.763</v>
       </c>
       <c r="AM4" t="n">
-        <v>13.8072755</v>
+        <v>6.70372541</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.766420254</v>
+        <v>0.372113307</v>
       </c>
       <c r="AO4" t="n">
         <v>50</v>
       </c>
       <c r="AP4" t="n">
-        <v>480.233479</v>
+        <v>600.825106</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-2510.42623</v>
+        <v>-2165.26207</v>
       </c>
       <c r="AR4" t="n">
-        <v>-12582473.7</v>
+        <v>-12302166.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>13.8072755</v>
+        <v>6.70372541</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.766420254</v>
+        <v>0.372113307</v>
       </c>
       <c r="AU4" t="n">
         <v>50</v>
       </c>
       <c r="AV4" t="n">
-        <v>265.505379</v>
+        <v>280.70843</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.99656935</v>
+        <v>2.10142203</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0305186425</v>
+        <v>0.0214019901</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.59658949</v>
+        <v>1.92997966</v>
       </c>
       <c r="AZ4" t="n">
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.99656935</v>
+        <v>2.10142203</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.0305186425</v>
+        <v>0.0214019901</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.59658949</v>
+        <v>1.92997966</v>
       </c>
       <c r="BD4" t="n">
-        <v>93.7899378</v>
+        <v>118.593558</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.99656935</v>
+        <v>2.10142203</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.07510998269999999</v>
+        <v>0.0608526899</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.59658949</v>
+        <v>1.92997966</v>
       </c>
       <c r="BH4" t="n">
-        <v>198.271934</v>
+        <v>191.243863</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.208425855</v>
+        <v>0.135602171</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.593680609</v>
+        <v>0.648298372</v>
       </c>
       <c r="BK4" t="n">
-        <v>2.99656935</v>
+        <v>2.10142203</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.07510998269999999</v>
+        <v>0.0608526899</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.59658949</v>
+        <v>1.92997966</v>
       </c>
       <c r="BN4" t="n">
-        <v>265.333212</v>
+        <v>280.708301</v>
       </c>
       <c r="BO4" t="n">
         <v>70</v>
@@ -1501,7 +1501,7 @@
         <v>50.07</v>
       </c>
       <c r="BR4" t="n">
-        <v>172.636984</v>
+        <v>178.257037</v>
       </c>
       <c r="BS4" t="n">
         <v>70</v>
@@ -1513,7 +1513,7 @@
         <v>50.05</v>
       </c>
       <c r="BV4" t="n">
-        <v>191.468286</v>
+        <v>195.190936</v>
       </c>
       <c r="BW4" t="n">
         <v>70</v>
@@ -1528,84 +1528,84 @@
         <v>264.0032</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.52</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7463729371759976</v>
+        <v>0.8200736864835444</v>
       </c>
       <c r="C5" t="n">
-        <v>4.707500170761763</v>
+        <v>2.885672304282382</v>
       </c>
       <c r="D5" t="n">
-        <v>17.47235361730437</v>
+        <v>11.64431179608452</v>
       </c>
       <c r="E5" t="n">
-        <v>6101.54789</v>
+        <v>7249.41643</v>
       </c>
       <c r="F5" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="G5" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="H5" t="n">
-        <v>19.49</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
         <v>1500</v>
       </c>
       <c r="J5" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="K5" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="L5" t="n">
         <v>1.034</v>
       </c>
       <c r="M5" t="n">
-        <v>642.22253</v>
+        <v>701.938526</v>
       </c>
       <c r="N5" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="O5" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="P5" t="n">
         <v>1.027</v>
       </c>
       <c r="Q5" t="n">
-        <v>380.246882</v>
+        <v>440.225456</v>
       </c>
       <c r="R5" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="S5" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="T5" t="n">
         <v>1.02</v>
       </c>
       <c r="U5" t="n">
-        <v>205.177438</v>
+        <v>207.426656</v>
       </c>
       <c r="V5" t="n">
-        <v>52.2461056</v>
+        <v>57.4051581</v>
       </c>
       <c r="W5" t="n">
-        <v>2.90009956</v>
+        <v>3.18647049</v>
       </c>
       <c r="X5" t="n">
         <v>50</v>
       </c>
       <c r="Y5" t="n">
-        <v>480.277892</v>
+        <v>600.90689</v>
       </c>
       <c r="Z5" t="n">
         <v>70</v>
@@ -1617,118 +1617,118 @@
         <v>50</v>
       </c>
       <c r="AC5" t="n">
-        <v>480.277892</v>
+        <v>600.90689</v>
       </c>
       <c r="AD5" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AE5" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AF5" t="n">
         <v>1.013</v>
       </c>
       <c r="AG5" t="n">
-        <v>190.310543</v>
+        <v>193.421988</v>
       </c>
       <c r="AH5" t="n">
-        <v>-258041.636</v>
+        <v>-241187.022</v>
       </c>
       <c r="AI5" t="n">
-        <v>-45403.882</v>
+        <v>-52167.3874</v>
       </c>
       <c r="AJ5" t="n">
         <v>32.9836374</v>
       </c>
       <c r="AK5" t="n">
-        <v>397.312928</v>
+        <v>399.666424</v>
       </c>
       <c r="AL5" t="n">
-        <v>-303015.221</v>
+        <v>-292921.759</v>
       </c>
       <c r="AM5" t="n">
-        <v>17.7538944</v>
+        <v>12.5948419</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.985490894</v>
+        <v>0.699119966</v>
       </c>
       <c r="AO5" t="n">
         <v>50</v>
       </c>
       <c r="AP5" t="n">
-        <v>480.277892</v>
+        <v>600.90689</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-2510.28807</v>
+        <v>-2165.04482</v>
       </c>
       <c r="AR5" t="n">
-        <v>-12582369.6</v>
+        <v>-12301976.3</v>
       </c>
       <c r="AS5" t="n">
-        <v>17.7538944</v>
+        <v>12.5948419</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.985490894</v>
+        <v>0.699119966</v>
       </c>
       <c r="AU5" t="n">
         <v>50</v>
       </c>
       <c r="AV5" t="n">
-        <v>283.959992</v>
+        <v>308.229581</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.40295905</v>
+        <v>2.93431721</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0448420568</v>
+        <v>0.0298846339</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.70750017</v>
+        <v>2.8856723</v>
       </c>
       <c r="AZ5" t="n">
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.40295905</v>
+        <v>2.93431721</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.0448420568</v>
+        <v>0.0298846339</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.70750017</v>
+        <v>2.8856723</v>
       </c>
       <c r="BD5" t="n">
-        <v>79.5804272</v>
+        <v>108.132275</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.40295905</v>
+        <v>2.93431721</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0828809651</v>
+        <v>0.09963481070000001</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.70750017</v>
+        <v>2.8856723</v>
       </c>
       <c r="BH5" t="n">
-        <v>230.460639</v>
+        <v>233.064134</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.388055577</v>
+        <v>0.06658892499999999</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.458958317</v>
+        <v>0.700058306</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.40295905</v>
+        <v>2.93431721</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0828809651</v>
+        <v>0.09963481070000001</v>
       </c>
       <c r="BM5" t="n">
-        <v>4.70750017</v>
+        <v>2.8856723</v>
       </c>
       <c r="BN5" t="n">
-        <v>283.569009</v>
+        <v>308.071276</v>
       </c>
       <c r="BO5" t="n">
         <v>70</v>
@@ -1740,7 +1740,7 @@
         <v>50.07</v>
       </c>
       <c r="BR5" t="n">
-        <v>172.407431</v>
+        <v>177.435742</v>
       </c>
       <c r="BS5" t="n">
         <v>70</v>
@@ -1752,7 +1752,7 @@
         <v>50.05</v>
       </c>
       <c r="BV5" t="n">
-        <v>191.295171</v>
+        <v>194.52543</v>
       </c>
       <c r="BW5" t="n">
         <v>70</v>
@@ -1767,84 +1767,84 @@
         <v>264.0032</v>
       </c>
       <c r="CA5" t="n">
-        <v>10.47</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8445040413014526</v>
+        <v>0.8323087127753783</v>
       </c>
       <c r="C6" t="n">
-        <v>3.311477561056016</v>
+        <v>1.760981968940269</v>
       </c>
       <c r="D6" t="n">
-        <v>22.6092244739748</v>
+        <v>14.96166389566484</v>
       </c>
       <c r="E6" t="n">
-        <v>6545.25404</v>
+        <v>7523.24696</v>
       </c>
       <c r="F6" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="G6" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="H6" t="n">
-        <v>19.49</v>
+        <v>15</v>
       </c>
       <c r="I6" t="n">
         <v>1500</v>
       </c>
       <c r="J6" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="K6" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="L6" t="n">
         <v>1.034</v>
       </c>
       <c r="M6" t="n">
-        <v>642.22253</v>
+        <v>701.938526</v>
       </c>
       <c r="N6" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="O6" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="P6" t="n">
         <v>1.027</v>
       </c>
       <c r="Q6" t="n">
-        <v>380.230066</v>
+        <v>440.02941</v>
       </c>
       <c r="R6" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="S6" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="T6" t="n">
         <v>1.02</v>
       </c>
       <c r="U6" t="n">
-        <v>205.096004</v>
+        <v>207.295539</v>
       </c>
       <c r="V6" t="n">
-        <v>59.1152829</v>
+        <v>58.2616099</v>
       </c>
       <c r="W6" t="n">
-        <v>3.28139684</v>
+        <v>3.23401079</v>
       </c>
       <c r="X6" t="n">
         <v>50</v>
       </c>
       <c r="Y6" t="n">
-        <v>480.237451</v>
+        <v>600.612261</v>
       </c>
       <c r="Z6" t="n">
         <v>70</v>
@@ -1856,118 +1856,118 @@
         <v>50</v>
       </c>
       <c r="AC6" t="n">
-        <v>480.237451</v>
+        <v>600.612261</v>
       </c>
       <c r="AD6" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AE6" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AF6" t="n">
         <v>1.013</v>
       </c>
       <c r="AG6" t="n">
-        <v>190.208031</v>
+        <v>193.277194</v>
       </c>
       <c r="AH6" t="n">
-        <v>-258041.636</v>
+        <v>-241187.022</v>
       </c>
       <c r="AI6" t="n">
-        <v>-45243.3423</v>
+        <v>-52047.0926</v>
       </c>
       <c r="AJ6" t="n">
         <v>32.9836374</v>
       </c>
       <c r="AK6" t="n">
-        <v>397.256703</v>
+        <v>399.624643</v>
       </c>
       <c r="AL6" t="n">
-        <v>-302854.737</v>
+        <v>-292801.506</v>
       </c>
       <c r="AM6" t="n">
-        <v>10.8847171</v>
+        <v>11.7383901</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.604193613</v>
+        <v>0.651579665</v>
       </c>
       <c r="AO6" t="n">
         <v>50</v>
       </c>
       <c r="AP6" t="n">
-        <v>480.237451</v>
+        <v>600.612261</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-2510.41388</v>
+        <v>-2165.82757</v>
       </c>
       <c r="AR6" t="n">
-        <v>-12582464.4</v>
+        <v>-12302660.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>10.8847171</v>
+        <v>11.7383901</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.604193613</v>
+        <v>0.651579665</v>
       </c>
       <c r="AU6" t="n">
         <v>50</v>
       </c>
       <c r="AV6" t="n">
-        <v>263.977846</v>
+        <v>275.140771</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.69742873</v>
+        <v>3.77027588</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.0580256187</v>
+        <v>0.0383984778</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.31147756</v>
+        <v>1.76098197</v>
       </c>
       <c r="AZ6" t="n">
         <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.69742873</v>
+        <v>3.77027588</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.0580256187</v>
+        <v>0.0383984778</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.31147756</v>
+        <v>1.76098197</v>
       </c>
       <c r="BD6" t="n">
-        <v>63.2549824</v>
+        <v>85.0028532</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.69742873</v>
+        <v>3.77027588</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.0907974018</v>
+        <v>0.10491602</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.31147756</v>
+        <v>1.76098197</v>
       </c>
       <c r="BH6" t="n">
-        <v>217.408612</v>
+        <v>217.764789</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.518755934</v>
+        <v>0.154656686</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.360933049</v>
+        <v>0.634007486</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.69742873</v>
+        <v>3.77027588</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.0907974018</v>
+        <v>0.10491602</v>
       </c>
       <c r="BM6" t="n">
-        <v>3.31147756</v>
+        <v>1.76098197</v>
       </c>
       <c r="BN6" t="n">
-        <v>257.771373</v>
+        <v>274.971243</v>
       </c>
       <c r="BO6" t="n">
         <v>70</v>
@@ -1979,7 +1979,7 @@
         <v>50.07</v>
       </c>
       <c r="BR6" t="n">
-        <v>172.285107</v>
+        <v>177.348013</v>
       </c>
       <c r="BS6" t="n">
         <v>70</v>
@@ -1991,7 +1991,7 @@
         <v>50.05</v>
       </c>
       <c r="BV6" t="n">
-        <v>191.194924</v>
+        <v>194.37739</v>
       </c>
       <c r="BW6" t="n">
         <v>70</v>
@@ -2006,84 +2006,84 @@
         <v>264.0032</v>
       </c>
       <c r="CA6" t="n">
-        <v>10.51</v>
+        <v>11.84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
-        <v>0.8975528527358717</v>
+        <v>0.8082046783566335</v>
       </c>
       <c r="C7" t="n">
-        <v>4.583545024561417</v>
+        <v>3.399072261731932</v>
       </c>
       <c r="D7" t="n">
-        <v>28.28524414949925</v>
+        <v>18.48274390113252</v>
       </c>
       <c r="E7" t="n">
-        <v>7443.89126</v>
+        <v>8241.35029</v>
       </c>
       <c r="F7" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="G7" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="H7" t="n">
-        <v>19.49</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
         <v>1500</v>
       </c>
       <c r="J7" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="K7" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="L7" t="n">
         <v>1.034</v>
       </c>
       <c r="M7" t="n">
-        <v>642.22253</v>
+        <v>701.938526</v>
       </c>
       <c r="N7" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="O7" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="P7" t="n">
         <v>1.027</v>
       </c>
       <c r="Q7" t="n">
-        <v>380.239811</v>
+        <v>440.18896</v>
       </c>
       <c r="R7" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="S7" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="T7" t="n">
         <v>1.02</v>
       </c>
       <c r="U7" t="n">
-        <v>204.944653</v>
+        <v>207.239384</v>
       </c>
       <c r="V7" t="n">
-        <v>62.8286997</v>
+        <v>56.5743275</v>
       </c>
       <c r="W7" t="n">
-        <v>3.4875228</v>
+        <v>3.14035238</v>
       </c>
       <c r="X7" t="n">
         <v>50</v>
       </c>
       <c r="Y7" t="n">
-        <v>480.260871</v>
+        <v>600.853259</v>
       </c>
       <c r="Z7" t="n">
         <v>70</v>
@@ -2095,118 +2095,118 @@
         <v>50</v>
       </c>
       <c r="AC7" t="n">
-        <v>480.260871</v>
+        <v>600.853259</v>
       </c>
       <c r="AD7" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AE7" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AF7" t="n">
         <v>1.013</v>
       </c>
       <c r="AG7" t="n">
-        <v>190.016841</v>
+        <v>193.197518</v>
       </c>
       <c r="AH7" t="n">
-        <v>-258041.636</v>
+        <v>-241187.022</v>
       </c>
       <c r="AI7" t="n">
-        <v>-44925.0662</v>
+        <v>-51793.4858</v>
       </c>
       <c r="AJ7" t="n">
         <v>32.9836374</v>
       </c>
       <c r="AK7" t="n">
-        <v>397.145137</v>
+        <v>399.536568</v>
       </c>
       <c r="AL7" t="n">
-        <v>-302536.573</v>
+        <v>-292547.987</v>
       </c>
       <c r="AM7" t="n">
-        <v>7.17130031</v>
+        <v>13.4256725</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.398067657</v>
+        <v>0.7452380709999999</v>
       </c>
       <c r="AO7" t="n">
         <v>50</v>
       </c>
       <c r="AP7" t="n">
-        <v>480.260871</v>
+        <v>600.853259</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-2510.34102</v>
+        <v>-2165.18728</v>
       </c>
       <c r="AR7" t="n">
-        <v>-12582409.5</v>
+        <v>-12302100.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.17130031</v>
+        <v>13.4256725</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.398067657</v>
+        <v>0.7452380709999999</v>
       </c>
       <c r="AU7" t="n">
         <v>50</v>
       </c>
       <c r="AV7" t="n">
-        <v>263.977846</v>
+        <v>289.027455</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.12776163</v>
+        <v>4.65757312</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0725928832</v>
+        <v>0.0474351807</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.58354502</v>
+        <v>3.39907226</v>
       </c>
       <c r="AZ7" t="n">
         <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.12776163</v>
+        <v>4.65757312</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0725928832</v>
+        <v>0.0474351807</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.58354502</v>
+        <v>3.39907226</v>
       </c>
       <c r="BD7" t="n">
-        <v>55.2047344</v>
+        <v>78.2010841</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.12776163</v>
+        <v>4.65757312</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.101763305</v>
+        <v>0.111515306</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.58354502</v>
+        <v>3.39907226</v>
       </c>
       <c r="BH7" t="n">
-        <v>223.150617</v>
+        <v>238.026282</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.617800387</v>
+        <v>0.233825652</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.28664971</v>
+        <v>0.574630761</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.12776163</v>
+        <v>4.65757312</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.101763305</v>
+        <v>0.111515306</v>
       </c>
       <c r="BM7" t="n">
-        <v>4.58354502</v>
+        <v>3.39907226</v>
       </c>
       <c r="BN7" t="n">
-        <v>256.494079</v>
+        <v>288.689228</v>
       </c>
       <c r="BO7" t="n">
         <v>70</v>
@@ -2218,7 +2218,7 @@
         <v>50.07</v>
       </c>
       <c r="BR7" t="n">
-        <v>172.042072</v>
+        <v>177.162897</v>
       </c>
       <c r="BS7" t="n">
         <v>70</v>
@@ -2230,7 +2230,7 @@
         <v>50.05</v>
       </c>
       <c r="BV7" t="n">
-        <v>191.008351</v>
+        <v>194.306112</v>
       </c>
       <c r="BW7" t="n">
         <v>70</v>
@@ -2245,84 +2245,84 @@
         <v>264.0032</v>
       </c>
       <c r="CA7" t="n">
-        <v>12.22</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7305348076770666</v>
+        <v>0.9428592057479144</v>
       </c>
       <c r="C8" t="n">
-        <v>1.533878780307815</v>
+        <v>3.140642101460692</v>
       </c>
       <c r="D8" t="n">
-        <v>33.82254248413494</v>
+        <v>21.93532335988839</v>
       </c>
       <c r="E8" t="n">
-        <v>10814.2879</v>
+        <v>6422.12296</v>
       </c>
       <c r="F8" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="G8" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="H8" t="n">
-        <v>19.49</v>
+        <v>15</v>
       </c>
       <c r="I8" t="n">
         <v>1500</v>
       </c>
       <c r="J8" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="K8" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="L8" t="n">
         <v>1.034</v>
       </c>
       <c r="M8" t="n">
-        <v>642.22253</v>
+        <v>701.938526</v>
       </c>
       <c r="N8" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="O8" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="P8" t="n">
         <v>1.027</v>
       </c>
       <c r="Q8" t="n">
-        <v>380.288506</v>
+        <v>440.192505</v>
       </c>
       <c r="R8" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="S8" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="T8" t="n">
         <v>1.02</v>
       </c>
       <c r="U8" t="n">
-        <v>204.372996</v>
+        <v>207.641065</v>
       </c>
       <c r="V8" t="n">
-        <v>51.1374365</v>
+        <v>66.0001444</v>
       </c>
       <c r="W8" t="n">
-        <v>2.83855908</v>
+        <v>3.66356473</v>
       </c>
       <c r="X8" t="n">
         <v>50</v>
       </c>
       <c r="Y8" t="n">
-        <v>480.376712</v>
+        <v>600.860592</v>
       </c>
       <c r="Z8" t="n">
         <v>70</v>
@@ -2334,58 +2334,58 @@
         <v>50</v>
       </c>
       <c r="AC8" t="n">
-        <v>480.376712</v>
+        <v>600.860592</v>
       </c>
       <c r="AD8" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AE8" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AF8" t="n">
         <v>1.013</v>
       </c>
       <c r="AG8" t="n">
-        <v>189.294318</v>
+        <v>193.677509</v>
       </c>
       <c r="AH8" t="n">
-        <v>-258041.636</v>
+        <v>-241187.022</v>
       </c>
       <c r="AI8" t="n">
-        <v>-43741.6532</v>
+        <v>-52474.2669</v>
       </c>
       <c r="AJ8" t="n">
         <v>32.9836374</v>
       </c>
       <c r="AK8" t="n">
-        <v>396.728989</v>
+        <v>399.773019</v>
       </c>
       <c r="AL8" t="n">
-        <v>-301353.576</v>
+        <v>-293228.532</v>
       </c>
       <c r="AM8" t="n">
-        <v>18.8625635</v>
+        <v>3.9998556</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.04703138</v>
+        <v>0.222025725</v>
       </c>
       <c r="AO8" t="n">
         <v>50</v>
       </c>
       <c r="AP8" t="n">
-        <v>480.376712</v>
+        <v>600.860592</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-2509.98068</v>
+        <v>-2165.1678</v>
       </c>
       <c r="AR8" t="n">
-        <v>-12582138</v>
+        <v>-12302083.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>18.8625635</v>
+        <v>3.9998556</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.04703138</v>
+        <v>0.222025725</v>
       </c>
       <c r="AU8" t="n">
         <v>50</v>
@@ -2394,58 +2394,58 @@
         <v>263.977846</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.52313734</v>
+        <v>5.52760851</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0868041252</v>
+        <v>0.0562960799</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.53387878</v>
+        <v>3.1406421</v>
       </c>
       <c r="AZ8" t="n">
         <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.52313734</v>
+        <v>5.52760851</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.0868041252</v>
+        <v>0.0562960799</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.53387878</v>
+        <v>3.1406421</v>
       </c>
       <c r="BD8" t="n">
-        <v>47.8927895</v>
+        <v>64.26691270000001</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.52313734</v>
+        <v>5.52760851</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.15062659</v>
+        <v>0.08934319189999999</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.53387878</v>
+        <v>3.1406421</v>
       </c>
       <c r="BH8" t="n">
-        <v>215.950581</v>
+        <v>216.102438</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.435049153</v>
+        <v>0.50681395</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.423713135</v>
+        <v>0.369889538</v>
       </c>
       <c r="BK8" t="n">
-        <v>8.52313734</v>
+        <v>5.52760851</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.15062659</v>
+        <v>0.08934319189999999</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.53387878</v>
+        <v>3.1406421</v>
       </c>
       <c r="BN8" t="n">
-        <v>243.085113</v>
+        <v>257.39017</v>
       </c>
       <c r="BO8" t="n">
         <v>70</v>
@@ -2457,7 +2457,7 @@
         <v>50.07</v>
       </c>
       <c r="BR8" t="n">
-        <v>171.131885</v>
+        <v>177.65932</v>
       </c>
       <c r="BS8" t="n">
         <v>70</v>
@@ -2469,7 +2469,7 @@
         <v>50.05</v>
       </c>
       <c r="BV8" t="n">
-        <v>190.303236</v>
+        <v>194.778824</v>
       </c>
       <c r="BW8" t="n">
         <v>70</v>
@@ -2484,84 +2484,84 @@
         <v>264.0032</v>
       </c>
       <c r="CA8" t="n">
-        <v>12.05</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9817568927124742</v>
+        <v>0.9402243389288264</v>
       </c>
       <c r="C9" t="n">
-        <v>4.282269349304877</v>
+        <v>3.964298257846063</v>
       </c>
       <c r="D9" t="n">
-        <v>38.79554270423673</v>
+        <v>25.88778192515885</v>
       </c>
       <c r="E9" t="n">
-        <v>3406.67226</v>
+        <v>7084.07171</v>
       </c>
       <c r="F9" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="G9" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="H9" t="n">
-        <v>19.49</v>
+        <v>15</v>
       </c>
       <c r="I9" t="n">
         <v>1500</v>
       </c>
       <c r="J9" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="K9" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="L9" t="n">
         <v>1.034</v>
       </c>
       <c r="M9" t="n">
-        <v>642.22253</v>
+        <v>701.938526</v>
       </c>
       <c r="N9" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="O9" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="P9" t="n">
         <v>1.027</v>
       </c>
       <c r="Q9" t="n">
-        <v>380.2231</v>
+        <v>440.196867</v>
       </c>
       <c r="R9" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="S9" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="T9" t="n">
         <v>1.02</v>
       </c>
       <c r="U9" t="n">
-        <v>205.632325</v>
+        <v>207.515313</v>
       </c>
       <c r="V9" t="n">
-        <v>68.7229825</v>
+        <v>65.8157037</v>
       </c>
       <c r="W9" t="n">
-        <v>3.81470521</v>
+        <v>3.65332672</v>
       </c>
       <c r="X9" t="n">
         <v>50</v>
       </c>
       <c r="Y9" t="n">
-        <v>480.221036</v>
+        <v>600.8672</v>
       </c>
       <c r="Z9" t="n">
         <v>70</v>
@@ -2573,118 +2573,118 @@
         <v>50</v>
       </c>
       <c r="AC9" t="n">
-        <v>480.221036</v>
+        <v>600.8672</v>
       </c>
       <c r="AD9" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AE9" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AF9" t="n">
         <v>1.013</v>
       </c>
       <c r="AG9" t="n">
-        <v>190.884864</v>
+        <v>193.525911</v>
       </c>
       <c r="AH9" t="n">
-        <v>-258041.636</v>
+        <v>-241187.022</v>
       </c>
       <c r="AI9" t="n">
-        <v>-46366.0062</v>
+        <v>-52226.8297</v>
       </c>
       <c r="AJ9" t="n">
         <v>32.9836374</v>
       </c>
       <c r="AK9" t="n">
-        <v>397.649279</v>
+        <v>399.68707</v>
       </c>
       <c r="AL9" t="n">
-        <v>-303977.009</v>
+        <v>-292981.181</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.27701751</v>
+        <v>4.18429627</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0708852435</v>
+        <v>0.232263738</v>
       </c>
       <c r="AO9" t="n">
         <v>50</v>
       </c>
       <c r="AP9" t="n">
-        <v>480.221036</v>
+        <v>600.8672</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-2510.46495</v>
+        <v>-2165.15025</v>
       </c>
       <c r="AR9" t="n">
-        <v>-12582502.9</v>
+        <v>-12302068.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.27701751</v>
+        <v>4.18429627</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.0708852435</v>
+        <v>0.232263738</v>
       </c>
       <c r="AU9" t="n">
         <v>50</v>
       </c>
       <c r="AV9" t="n">
-        <v>159.934944</v>
+        <v>263.977846</v>
       </c>
       <c r="AW9" t="n">
-        <v>9.77631231</v>
+        <v>6.52361131</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.09956712</v>
+        <v>0.0664398977</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.28226935</v>
+        <v>3.96429826</v>
       </c>
       <c r="AZ9" t="n">
         <v>15</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.77631231</v>
+        <v>6.52361131</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.09956712</v>
+        <v>0.0664398977</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.28226935</v>
+        <v>3.96429826</v>
       </c>
       <c r="BD9" t="n">
-        <v>34.6313907</v>
+        <v>58.2730663</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.77631231</v>
+        <v>6.52361131</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.100158611</v>
+        <v>0.09741260710000001</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.28226935</v>
+        <v>3.96429826</v>
       </c>
       <c r="BH9" t="n">
-        <v>156.632792</v>
+        <v>221.013738</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.992125939</v>
+        <v>0.576061589</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.00590554595</v>
+        <v>0.317953808</v>
       </c>
       <c r="BK9" t="n">
-        <v>9.77631231</v>
+        <v>6.52361131</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.100158611</v>
+        <v>0.09741260710000001</v>
       </c>
       <c r="BM9" t="n">
-        <v>4.28226935</v>
+        <v>3.96429826</v>
       </c>
       <c r="BN9" t="n">
-        <v>159.934632</v>
+        <v>257.013776</v>
       </c>
       <c r="BO9" t="n">
         <v>70</v>
@@ -2696,7 +2696,7 @@
         <v>50.07</v>
       </c>
       <c r="BR9" t="n">
-        <v>173.137022</v>
+        <v>177.479074</v>
       </c>
       <c r="BS9" t="n">
         <v>70</v>
@@ -2708,7 +2708,7 @@
         <v>50.05</v>
       </c>
       <c r="BV9" t="n">
-        <v>191.855519</v>
+        <v>194.630684</v>
       </c>
       <c r="BW9" t="n">
         <v>70</v>
@@ -2723,84 +2723,84 @@
         <v>264.0032</v>
       </c>
       <c r="CA9" t="n">
-        <v>11.54</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9180373935351041</v>
+        <v>0.9735053067430608</v>
       </c>
       <c r="C10" t="n">
-        <v>1.059187848029279</v>
+        <v>1.170855651306417</v>
       </c>
       <c r="D10" t="n">
-        <v>44.39478542358398</v>
+        <v>29.29209477569001</v>
       </c>
       <c r="E10" t="n">
-        <v>12616.5446</v>
+        <v>5229.81645</v>
       </c>
       <c r="F10" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="G10" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="H10" t="n">
-        <v>19.49</v>
+        <v>15</v>
       </c>
       <c r="I10" t="n">
         <v>1500</v>
       </c>
       <c r="J10" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="K10" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="L10" t="n">
         <v>1.034</v>
       </c>
       <c r="M10" t="n">
-        <v>642.22253</v>
+        <v>701.938526</v>
       </c>
       <c r="N10" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="O10" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="P10" t="n">
         <v>1.027</v>
       </c>
       <c r="Q10" t="n">
-        <v>380.266286</v>
+        <v>440.077089</v>
       </c>
       <c r="R10" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="S10" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="T10" t="n">
         <v>1.02</v>
       </c>
       <c r="U10" t="n">
-        <v>204.064499</v>
+        <v>207.774982</v>
       </c>
       <c r="V10" t="n">
-        <v>64.2626175</v>
+        <v>68.1453715</v>
       </c>
       <c r="W10" t="n">
-        <v>3.56711733</v>
+        <v>3.78264293</v>
       </c>
       <c r="X10" t="n">
         <v>50</v>
       </c>
       <c r="Y10" t="n">
-        <v>480.324036</v>
+        <v>600.684926</v>
       </c>
       <c r="Z10" t="n">
         <v>70</v>
@@ -2812,118 +2812,118 @@
         <v>50</v>
       </c>
       <c r="AC10" t="n">
-        <v>480.324036</v>
+        <v>600.684926</v>
       </c>
       <c r="AD10" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AE10" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AF10" t="n">
         <v>1.013</v>
       </c>
       <c r="AG10" t="n">
-        <v>188.904518</v>
+        <v>193.849167</v>
       </c>
       <c r="AH10" t="n">
-        <v>-258041.636</v>
+        <v>-241187.022</v>
       </c>
       <c r="AI10" t="n">
-        <v>-43108.2037</v>
+        <v>-52910.775</v>
       </c>
       <c r="AJ10" t="n">
         <v>32.9836374</v>
       </c>
       <c r="AK10" t="n">
-        <v>396.505213</v>
+        <v>399.924673</v>
       </c>
       <c r="AL10" t="n">
-        <v>-300720.35</v>
+        <v>-293664.888</v>
       </c>
       <c r="AM10" t="n">
-        <v>5.73738245</v>
+        <v>1.85462853</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.318473121</v>
+        <v>0.102947527</v>
       </c>
       <c r="AO10" t="n">
         <v>50</v>
       </c>
       <c r="AP10" t="n">
-        <v>480.324036</v>
+        <v>600.684926</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-2510.14453</v>
+        <v>-2165.63449</v>
       </c>
       <c r="AR10" t="n">
-        <v>-12582261.4</v>
+        <v>-12302491.7</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.73738245</v>
+        <v>1.85462853</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.318473121</v>
+        <v>0.102947527</v>
       </c>
       <c r="AU10" t="n">
         <v>50</v>
       </c>
       <c r="AV10" t="n">
-        <v>239.289897</v>
+        <v>183.670338</v>
       </c>
       <c r="AW10" t="n">
-        <v>11.1872977</v>
+        <v>7.38148372</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.11393734</v>
+        <v>0.0751769227</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.05918785</v>
+        <v>1.17085565</v>
       </c>
       <c r="AZ10" t="n">
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.1872977</v>
+        <v>7.38148372</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.11393734</v>
+        <v>0.0751769227</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.05918785</v>
+        <v>1.17085565</v>
       </c>
       <c r="BD10" t="n">
-        <v>39.0208559</v>
+        <v>42.43879</v>
       </c>
       <c r="BE10" t="n">
-        <v>11.1872977</v>
+        <v>7.38148372</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.179704041</v>
+        <v>0.0855024309</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.05918785</v>
+        <v>1.17085565</v>
       </c>
       <c r="BH10" t="n">
-        <v>204.58211</v>
+        <v>157.860976</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.512036932</v>
+        <v>0.838983008</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.365972301</v>
+        <v>0.120762744</v>
       </c>
       <c r="BK10" t="n">
-        <v>11.1872977</v>
+        <v>7.38148372</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.179704041</v>
+        <v>0.0855024309</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.05918785</v>
+        <v>1.17085565</v>
       </c>
       <c r="BN10" t="n">
-        <v>224.784192</v>
+        <v>183.669802</v>
       </c>
       <c r="BO10" t="n">
         <v>70</v>
@@ -2935,7 +2935,7 @@
         <v>50.07</v>
       </c>
       <c r="BR10" t="n">
-        <v>170.640048</v>
+        <v>177.976799</v>
       </c>
       <c r="BS10" t="n">
         <v>70</v>
@@ -2947,7 +2947,7 @@
         <v>50.05</v>
       </c>
       <c r="BV10" t="n">
-        <v>189.922812</v>
+        <v>194.940193</v>
       </c>
       <c r="BW10" t="n">
         <v>70</v>
@@ -2962,84 +2962,84 @@
         <v>264.0032</v>
       </c>
       <c r="CA10" t="n">
-        <v>11.48</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="B11" t="n">
-        <v>0.9008663797459928</v>
+        <v>0.8103672278964829</v>
       </c>
       <c r="C11" t="n">
-        <v>3.353523655065142</v>
+        <v>4.267408673977911</v>
       </c>
       <c r="D11" t="n">
-        <v>49.5890465596561</v>
+        <v>32.79468230066439</v>
       </c>
       <c r="E11" t="n">
-        <v>12251.8618</v>
+        <v>9245.637580000001</v>
       </c>
       <c r="F11" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="G11" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="H11" t="n">
-        <v>19.49</v>
+        <v>15</v>
       </c>
       <c r="I11" t="n">
         <v>1500</v>
       </c>
       <c r="J11" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="K11" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="L11" t="n">
         <v>1.034</v>
       </c>
       <c r="M11" t="n">
-        <v>642.22253</v>
+        <v>701.938526</v>
       </c>
       <c r="N11" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="O11" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="P11" t="n">
         <v>1.027</v>
       </c>
       <c r="Q11" t="n">
-        <v>380.277944</v>
+        <v>440.307263</v>
       </c>
       <c r="R11" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="S11" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="T11" t="n">
         <v>1.02</v>
       </c>
       <c r="U11" t="n">
-        <v>204.11379</v>
+        <v>207.046985</v>
       </c>
       <c r="V11" t="n">
-        <v>63.0606466</v>
+        <v>56.725706</v>
       </c>
       <c r="W11" t="n">
-        <v>3.50039781</v>
+        <v>3.14875517</v>
       </c>
       <c r="X11" t="n">
         <v>50</v>
       </c>
       <c r="Y11" t="n">
-        <v>480.351991</v>
+        <v>601.034341</v>
       </c>
       <c r="Z11" t="n">
         <v>70</v>
@@ -3051,58 +3051,58 @@
         <v>50</v>
       </c>
       <c r="AC11" t="n">
-        <v>480.351991</v>
+        <v>601.034341</v>
       </c>
       <c r="AD11" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AE11" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AF11" t="n">
         <v>1.013</v>
       </c>
       <c r="AG11" t="n">
-        <v>188.968323</v>
+        <v>192.962381</v>
       </c>
       <c r="AH11" t="n">
-        <v>-258041.636</v>
+        <v>-241187.022</v>
       </c>
       <c r="AI11" t="n">
-        <v>-43237.0181</v>
+        <v>-51429.9666</v>
       </c>
       <c r="AJ11" t="n">
         <v>32.9836374</v>
       </c>
       <c r="AK11" t="n">
-        <v>396.550784</v>
+        <v>399.410335</v>
       </c>
       <c r="AL11" t="n">
-        <v>-300849.119</v>
+        <v>-292184.594</v>
       </c>
       <c r="AM11" t="n">
-        <v>6.93935342</v>
+        <v>13.274294</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.385192649</v>
+        <v>0.7368352889999999</v>
       </c>
       <c r="AO11" t="n">
         <v>50</v>
       </c>
       <c r="AP11" t="n">
-        <v>480.351991</v>
+        <v>601.034341</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-2510.05757</v>
+        <v>-2164.70629</v>
       </c>
       <c r="AR11" t="n">
-        <v>-12582195.9</v>
+        <v>-12301680.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.93935342</v>
+        <v>13.274294</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.385192649</v>
+        <v>0.7368352889999999</v>
       </c>
       <c r="AU11" t="n">
         <v>50</v>
@@ -3111,58 +3111,58 @@
         <v>263.977846</v>
       </c>
       <c r="AW11" t="n">
-        <v>12.4962295</v>
+        <v>8.264120930000001</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.127268191</v>
+        <v>0.0841661655</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.35352366</v>
+        <v>4.26740867</v>
       </c>
       <c r="AZ11" t="n">
         <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.4962295</v>
+        <v>8.264120930000001</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.127268191</v>
+        <v>0.0841661655</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.35352366</v>
+        <v>4.26740867</v>
       </c>
       <c r="BD11" t="n">
-        <v>38.2960981</v>
+        <v>51.1723534</v>
       </c>
       <c r="BE11" t="n">
-        <v>12.4962295</v>
+        <v>8.264120930000001</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.168232067</v>
+        <v>0.124509057</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.35352366</v>
+        <v>4.26740867</v>
       </c>
       <c r="BH11" t="n">
-        <v>220.638239</v>
+        <v>230.754598</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.675338349</v>
+        <v>0.567979042</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.243496239</v>
+        <v>0.324015719</v>
       </c>
       <c r="BK11" t="n">
-        <v>12.4962295</v>
+        <v>8.264120930000001</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.168232067</v>
+        <v>0.124509057</v>
       </c>
       <c r="BM11" t="n">
-        <v>3.35352366</v>
+        <v>4.26740867</v>
       </c>
       <c r="BN11" t="n">
-        <v>239.892185</v>
+        <v>260.242537</v>
       </c>
       <c r="BO11" t="n">
         <v>70</v>
@@ -3174,7 +3174,7 @@
         <v>50.07</v>
       </c>
       <c r="BR11" t="n">
-        <v>170.740346</v>
+        <v>176.897157</v>
       </c>
       <c r="BS11" t="n">
         <v>70</v>
@@ -3186,7 +3186,7 @@
         <v>50.05</v>
       </c>
       <c r="BV11" t="n">
-        <v>189.983617</v>
+        <v>194.075773</v>
       </c>
       <c r="BW11" t="n">
         <v>70</v>
@@ -3201,7 +3201,1202 @@
         <v>264.0032</v>
       </c>
       <c r="CA11" t="n">
-        <v>11.37</v>
+        <v>11.21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>34</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.7950268239107251</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.482847560676458</v>
+      </c>
+      <c r="D12" t="n">
+        <v>36.17239762761049</v>
+      </c>
+      <c r="E12" t="n">
+        <v>11058.2191</v>
+      </c>
+      <c r="F12" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="H12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J12" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="K12" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="M12" t="n">
+        <v>701.938526</v>
+      </c>
+      <c r="N12" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="O12" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>440.312613</v>
+      </c>
+      <c r="R12" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="S12" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="U12" t="n">
+        <v>206.708648</v>
+      </c>
+      <c r="V12" t="n">
+        <v>55.6518777</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.08914864</v>
+      </c>
+      <c r="X12" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>601.042435</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>601.042435</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>192.554187</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-241187.022</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-50756.5596</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>32.9836374</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>399.176508</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-291511.421</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>14.3481223</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.796441816</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>601.042435</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-2164.6848</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-12301661.6</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>14.3481223</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.796441816</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>263.977846</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>9.115290870000001</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.0928349291</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>2.48284756</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>9.115290870000001</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.0928349291</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.48284756</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>47.2877215</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>9.115290870000001</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0.15090049</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2.48284756</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>225.929601</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0.486941707</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.38479372</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>9.115290870000001</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0.15090049</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>2.48284756</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>252.247963</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>70</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>176.403595</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>70</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>193.677153</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>70</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>264.0032</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>12.26</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.8664054542875337</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.790033964204278</v>
+      </c>
+      <c r="D13" t="n">
+        <v>39.4907603171984</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10910.664</v>
+      </c>
+      <c r="F13" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="H13" t="n">
+        <v>15</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J13" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="K13" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="M13" t="n">
+        <v>701.938526</v>
+      </c>
+      <c r="N13" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="O13" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>440.230767</v>
+      </c>
+      <c r="R13" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="S13" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="U13" t="n">
+        <v>206.797117</v>
+      </c>
+      <c r="V13" t="n">
+        <v>60.6483818</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.36649676</v>
+      </c>
+      <c r="X13" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>600.918544</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>600.918544</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>192.659289</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-241187.022</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-50803.8459</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>32.9836374</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>399.192927</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-291558.691</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>9.351618200000001</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.519093692</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>600.918544</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-2165.01386</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-12301949.3</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>9.351618200000001</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.519093692</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>263.977846</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>9.9515042</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.101351367</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>2.79003396</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>9.9515042</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.101351367</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.79003396</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>44.2740744</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>9.9515042</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0.149420184</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.79003396</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>222.947197</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0.571063597</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.321702302</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>9.9515042</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.149420184</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>2.79003396</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>247.003303</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>70</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>176.438309</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>70</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>193.783987</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>70</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>264.0032</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>10.87</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>51</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.8263192028348481</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4.816341120505886</v>
+      </c>
+      <c r="D14" t="n">
+        <v>42.80554159781327</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10941.2402</v>
+      </c>
+      <c r="F14" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="H14" t="n">
+        <v>15</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J14" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="K14" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="M14" t="n">
+        <v>701.938526</v>
+      </c>
+      <c r="N14" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="O14" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>440.228984</v>
+      </c>
+      <c r="R14" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="S14" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="U14" t="n">
+        <v>206.789667</v>
+      </c>
+      <c r="V14" t="n">
+        <v>57.8423442</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.21073801</v>
+      </c>
+      <c r="X14" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>600.915844</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>600.915844</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>192.650373</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-241187.022</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-50792.3348</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>32.9836374</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>399.18893</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-291547.184</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>12.1576558</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.674852448</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>600.915844</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-2165.02104</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-12301955.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>12.1576558</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.674852448</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>263.977846</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>10.786815</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.109858613</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>4.81634112</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>10.786815</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.109858613</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.81634112</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>42.9559236</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>10.786815</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0.147174403</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>4.81634112</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>229.456559</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0.661935862</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.253548103</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>10.786815</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.147174403</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>4.81634112</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>252.2795</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>70</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>176.429859</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>70</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>193.775269</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>70</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>264.0032</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.912245780135622</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.270373373054419</v>
+      </c>
+      <c r="D15" t="n">
+        <v>46.46015970206421</v>
+      </c>
+      <c r="E15" t="n">
+        <v>13386.3887</v>
+      </c>
+      <c r="F15" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="G15" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="H15" t="n">
+        <v>15</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J15" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="K15" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="M15" t="n">
+        <v>701.938526</v>
+      </c>
+      <c r="N15" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="O15" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>440.204988</v>
+      </c>
+      <c r="R15" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="S15" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="U15" t="n">
+        <v>206.333036</v>
+      </c>
+      <c r="V15" t="n">
+        <v>63.8572046</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.5446135</v>
+      </c>
+      <c r="X15" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>600.879094</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>600.879094</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>192.09917</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-241187.022</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-49885.154</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>32.9836374</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>398.8739</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-290640.318</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>6.14279539</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.340976959</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>600.879094</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-2165.11866</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-12302040.8</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>6.14279539</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.340976959</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>263.977846</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>11.7077633</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.119238035</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.27037337</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>11.7077633</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.119238035</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.27037337</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>38.7351853</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>11.7077633</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0.188054152</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.27037337</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>211.309658</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0.512082979</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.365937766</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>11.7077633</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.188054152</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.27037337</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>231.043849</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>70</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>175.762286</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>70</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>193.238077</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>70</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>264.0032</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>12.01</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>84</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.9008663797459928</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.353523655065142</v>
+      </c>
+      <c r="D16" t="n">
+        <v>49.5890465596561</v>
+      </c>
+      <c r="E16" t="n">
+        <v>12468.5687</v>
+      </c>
+      <c r="F16" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="G16" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="H16" t="n">
+        <v>15</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J16" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="K16" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="M16" t="n">
+        <v>701.938526</v>
+      </c>
+      <c r="N16" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="O16" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>440.24312</v>
+      </c>
+      <c r="R16" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="S16" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="U16" t="n">
+        <v>206.503982</v>
+      </c>
+      <c r="V16" t="n">
+        <v>63.0606466</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.50039781</v>
+      </c>
+      <c r="X16" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>600.9372499999999</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>600.9372499999999</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>192.305412</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-241187.022</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-50227.7557</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>32.9836374</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>398.992879</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-290982.801</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>6.93935342</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.385192649</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>600.9372499999999</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-2164.96418</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-12301905.8</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>6.93935342</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.385192649</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>263.977846</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>12.4962295</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.127268191</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>3.35352366</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>12.4962295</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.127268191</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>3.35352366</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>38.4839982</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>12.4962295</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0.170570507</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>3.35352366</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>222.341729</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0.661509941</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.253867544</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>12.4962295</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.170570507</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>3.35352366</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>241.684571</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>70</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>176.014781</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>70</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>193.438281</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>70</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>264.0032</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>10.07</v>
       </c>
     </row>
   </sheetData>
@@ -3249,7 +4444,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
